--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484146_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484146_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.4379</v>
+        <v>4.3116</v>
       </c>
       <c r="E2" t="n">
-        <v>3.2563</v>
+        <v>2.2984</v>
       </c>
       <c r="F2" t="n">
-        <v>2.1815</v>
+        <v>2.0132</v>
       </c>
       <c r="G2" t="n">
         <v>0.4569</v>
@@ -610,13 +610,13 @@
         <v>1.3887</v>
       </c>
       <c r="S2" t="n">
-        <v>1.6278</v>
+        <v>0.5016</v>
       </c>
       <c r="T2" t="n">
-        <v>1.1054</v>
+        <v>0.1475</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5224</v>
+        <v>0.3541</v>
       </c>
       <c r="V2" t="n">
         <v>2.9564</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.1067</v>
+        <v>0.6724</v>
       </c>
       <c r="E3" t="n">
-        <v>1.7151</v>
+        <v>2.1856</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.8218</v>
+        <v>-1.5132</v>
       </c>
       <c r="G3" t="n">
         <v>0.5113</v>
@@ -688,13 +688,13 @@
         <v>1.1903</v>
       </c>
       <c r="S3" t="n">
-        <v>-2.0388</v>
+        <v>-1.2598</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.1846</v>
+        <v>-0.7141</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.8542999999999999</v>
+        <v>-0.5457</v>
       </c>
       <c r="V3" t="n">
         <v>2.2144</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.1488</v>
+        <v>-0.2853</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.3571</v>
+        <v>0.0113</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2083</v>
+        <v>-0.2967</v>
       </c>
       <c r="G4" t="n">
         <v>-1.8078</v>
@@ -766,13 +766,13 @@
         <v>1.7855</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0317</v>
+        <v>-0.1049</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.1902</v>
+        <v>-0.8217</v>
       </c>
       <c r="U4" t="n">
-        <v>1.2218</v>
+        <v>0.7168</v>
       </c>
       <c r="V4" t="n">
         <v>2.8176</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.474</v>
+        <v>-0.5301</v>
       </c>
       <c r="E5" t="n">
         <v>-0.1467</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3273</v>
+        <v>-0.3834</v>
       </c>
       <c r="G5" t="n">
         <v>-0.3515</v>
@@ -844,13 +844,13 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1224</v>
+        <v>-0.1786</v>
       </c>
       <c r="T5" t="n">
         <v>-0.187</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0646</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.6605</v>
+        <v>-0.5483</v>
       </c>
       <c r="E6" t="n">
         <v>-0.3337</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3268</v>
+        <v>-0.2145</v>
       </c>
       <c r="G6" t="n">
         <v>-0.2876</v>
@@ -922,13 +922,13 @@
         <v>0.1984</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5713</v>
+        <v>-0.4591</v>
       </c>
       <c r="T6" t="n">
         <v>-0.3741</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1973</v>
+        <v>-0.08500000000000001</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.0273</v>
+        <v>-0.7314000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.5578</v>
+        <v>-0.1497</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.4695</v>
+        <v>-0.5817</v>
       </c>
       <c r="G7" t="n">
         <v>-1.0492</v>
@@ -1000,13 +1000,13 @@
         <v>0.3968</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1089</v>
+        <v>0.187</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6235000000000001</v>
+        <v>-0.2153</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5145999999999999</v>
+        <v>0.4024</v>
       </c>
       <c r="V7" t="n">
         <v>-0.266</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.3758</v>
+        <v>-1.339</v>
       </c>
       <c r="E9" t="n">
-        <v>0.434</v>
+        <v>0.1902</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.8098</v>
+        <v>-1.5293</v>
       </c>
       <c r="G9" t="n">
         <v>3.7177</v>
@@ -1156,13 +1156,13 @@
         <v>1.3887</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0623</v>
+        <v>-0.0255</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0112</v>
+        <v>-0.2549</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0511</v>
+        <v>0.2294</v>
       </c>
       <c r="V9" t="n">
         <v>-0.4683</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.9237</v>
+        <v>-2.2171</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.7921</v>
+        <v>-1.2819</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.1316</v>
+        <v>-0.9352</v>
       </c>
       <c r="G10" t="n">
         <v>-3.9141</v>
@@ -1234,13 +1234,13 @@
         <v>1.1903</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.5412</v>
+        <v>-0.8347</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.1846</v>
+        <v>-0.6744</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3566</v>
+        <v>-0.1602</v>
       </c>
       <c r="V10" t="n">
         <v>1.3414</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>P. BARBECHO GARCIA</t>
+          <t>D. FONT RODRIGUEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.3215</v>
+        <v>-3.4728</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.2974</v>
+        <v>-2.8265</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.0241</v>
+        <v>-0.6463</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.12</v>
+        <v>-5.1647</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.5953</v>
+        <v>-1.9103</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5247000000000001</v>
+        <v>-3.2545</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.3954</v>
+        <v>-3.2694</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.3954</v>
+        <v>-1.1938</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>-2.0756</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.7246</v>
+        <v>-1.8953</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.1999</v>
+        <v>-0.7165</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.5247000000000001</v>
+        <v>-1.1788</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.5871</v>
+        <v>-0.9919</v>
       </c>
       <c r="Q11" t="n">
         <v>-1.9838</v>
       </c>
       <c r="R11" t="n">
-        <v>0.3968</v>
+        <v>0.9919</v>
       </c>
       <c r="S11" t="n">
-        <v>0.8536</v>
+        <v>-0.2013</v>
       </c>
       <c r="T11" t="n">
-        <v>0.5499000000000001</v>
+        <v>-0.5894</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3037</v>
+        <v>0.3881</v>
       </c>
       <c r="V11" t="n">
-        <v>0.532</v>
+        <v>2.8851</v>
       </c>
       <c r="W11" t="n">
-        <v>0.532</v>
+        <v>3.0162</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-0.1311</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>D. FONT RODRIGUEZ</t>
+          <t>P. BARBECHO GARCIA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.1116</v>
+        <v>-4.2601</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.297</v>
+        <v>-3.0116</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.8146</v>
+        <v>-1.2485</v>
       </c>
       <c r="G12" t="n">
-        <v>-5.1647</v>
+        <v>-3.12</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.9103</v>
+        <v>-2.5953</v>
       </c>
       <c r="I12" t="n">
-        <v>-3.2545</v>
+        <v>-0.5247000000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>-3.2694</v>
+        <v>-1.3954</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.1938</v>
+        <v>-1.3954</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.0756</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.8953</v>
+        <v>-1.7246</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.7165</v>
+        <v>-1.1999</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.1788</v>
+        <v>-0.5247000000000001</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.9919</v>
+        <v>-1.5871</v>
       </c>
       <c r="Q12" t="n">
         <v>-1.9838</v>
       </c>
       <c r="R12" t="n">
-        <v>0.9919</v>
+        <v>0.3968</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.8401</v>
+        <v>-0.08500000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.0599</v>
+        <v>-0.1643</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2198</v>
+        <v>0.0793</v>
       </c>
       <c r="V12" t="n">
-        <v>2.8851</v>
+        <v>0.532</v>
       </c>
       <c r="W12" t="n">
-        <v>3.0162</v>
+        <v>0.532</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.1311</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-9.740500000000001</v>
+        <v>-9.428599999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.3984</v>
+        <v>-3.0866</v>
       </c>
       <c r="F13" t="n">
-        <v>-6.3422</v>
+        <v>-6.3421</v>
       </c>
       <c r="G13" t="n">
         <v>-11.9751</v>
@@ -1441,10 +1441,10 @@
         <v>-9.3279</v>
       </c>
       <c r="J13" t="n">
-        <v>3.370799999999998</v>
+        <v>3.370799999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>3.5334</v>
+        <v>3.533400000000001</v>
       </c>
       <c r="L13" t="n">
         <v>-0.1624999999999999</v>
@@ -1456,25 +1456,25 @@
         <v>-6.180899999999999</v>
       </c>
       <c r="O13" t="n">
-        <v>-9.1652</v>
+        <v>-9.165199999999999</v>
       </c>
       <c r="P13" t="n">
-        <v>-6.9433</v>
+        <v>-6.943300000000001</v>
       </c>
       <c r="Q13" t="n">
         <v>-15.8706</v>
       </c>
       <c r="R13" t="n">
-        <v>8.927399999999999</v>
+        <v>8.9274</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.8342</v>
+        <v>-2.5226</v>
       </c>
       <c r="T13" t="n">
-        <v>-4.2221</v>
+        <v>-3.91</v>
       </c>
       <c r="U13" t="n">
-        <v>1.3876</v>
+        <v>1.3877</v>
       </c>
       <c r="V13" t="n">
         <v>12.0126</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.5523</v>
+        <v>5.6162</v>
       </c>
       <c r="E14" t="n">
-        <v>3.5123</v>
+        <v>2.492</v>
       </c>
       <c r="F14" t="n">
-        <v>3.04</v>
+        <v>3.1242</v>
       </c>
       <c r="G14" t="n">
         <v>2.3876</v>
@@ -1546,13 +1546,13 @@
         <v>0.7935</v>
       </c>
       <c r="S14" t="n">
-        <v>1.4902</v>
+        <v>0.5541</v>
       </c>
       <c r="T14" t="n">
-        <v>1.3548</v>
+        <v>0.3345</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1354</v>
+        <v>0.2196</v>
       </c>
       <c r="V14" t="n">
         <v>1.881</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.7825</v>
+        <v>4.6167</v>
       </c>
       <c r="E15" t="n">
-        <v>3.5237</v>
+        <v>3.2176</v>
       </c>
       <c r="F15" t="n">
-        <v>1.2588</v>
+        <v>1.3991</v>
       </c>
       <c r="G15" t="n">
         <v>5.7083</v>
@@ -1624,13 +1624,13 @@
         <v>1.1903</v>
       </c>
       <c r="S15" t="n">
-        <v>0.3996</v>
+        <v>0.2338</v>
       </c>
       <c r="T15" t="n">
-        <v>0.4366</v>
+        <v>0.1305</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0369</v>
+        <v>0.1034</v>
       </c>
       <c r="V15" t="n">
         <v>-0.532</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.2403</v>
+        <v>2.9928</v>
       </c>
       <c r="E16" t="n">
-        <v>1.1232</v>
+        <v>1.7354</v>
       </c>
       <c r="F16" t="n">
-        <v>1.1172</v>
+        <v>1.2574</v>
       </c>
       <c r="G16" t="n">
         <v>2.6517</v>
@@ -1702,13 +1702,13 @@
         <v>1.9838</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.6773</v>
+        <v>0.0751</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.1222</v>
+        <v>-0.51</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4449</v>
+        <v>0.5852000000000001</v>
       </c>
       <c r="V16" t="n">
         <v>0.266</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. ELLENA VICENTE</t>
+          <t>J. RIERA MESTRE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.411</v>
+        <v>0.9438</v>
       </c>
       <c r="E17" t="n">
-        <v>1.7138</v>
+        <v>1.0541</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.3029</v>
+        <v>-0.1102</v>
       </c>
       <c r="G17" t="n">
-        <v>1.0042</v>
+        <v>1.2404</v>
       </c>
       <c r="H17" t="n">
-        <v>0.3525</v>
+        <v>-0.5643</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6516</v>
+        <v>1.8047</v>
       </c>
       <c r="J17" t="n">
-        <v>1.3911</v>
+        <v>2.6387</v>
       </c>
       <c r="K17" t="n">
-        <v>0.746</v>
+        <v>0.711</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6451</v>
+        <v>1.9278</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.387</v>
+        <v>-1.3983</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.3935</v>
+        <v>-1.2753</v>
       </c>
       <c r="O17" t="n">
-        <v>0.0065</v>
+        <v>-0.123</v>
       </c>
       <c r="P17" t="n">
-        <v>0.5952</v>
+        <v>0.1984</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-0.9919</v>
       </c>
       <c r="R17" t="n">
-        <v>0.5952</v>
+        <v>1.1903</v>
       </c>
       <c r="S17" t="n">
-        <v>0.7521</v>
+        <v>-0.4237</v>
       </c>
       <c r="T17" t="n">
-        <v>0.0567</v>
+        <v>-0.5214</v>
       </c>
       <c r="U17" t="n">
-        <v>0.6954</v>
+        <v>0.0978</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.9405</v>
+        <v>-0.0713</v>
       </c>
       <c r="W17" t="n">
-        <v>0.266</v>
+        <v>-0.0713</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.2065</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. RIERA MESTRE</t>
+          <t>A. ELLENA VICENTE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.7015</v>
+        <v>0.8983</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9520999999999999</v>
+        <v>1.5098</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.2505</v>
+        <v>-0.6115</v>
       </c>
       <c r="G18" t="n">
-        <v>1.2404</v>
+        <v>1.0042</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.5643</v>
+        <v>0.3525</v>
       </c>
       <c r="I18" t="n">
-        <v>1.8047</v>
+        <v>0.6516</v>
       </c>
       <c r="J18" t="n">
-        <v>2.6387</v>
+        <v>1.3911</v>
       </c>
       <c r="K18" t="n">
-        <v>0.711</v>
+        <v>0.746</v>
       </c>
       <c r="L18" t="n">
-        <v>1.9278</v>
+        <v>0.6451</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.3983</v>
+        <v>-0.387</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.2753</v>
+        <v>-0.3935</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.123</v>
+        <v>0.0065</v>
       </c>
       <c r="P18" t="n">
-        <v>0.1984</v>
+        <v>0.5952</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9919</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1903</v>
+        <v>0.5952</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.666</v>
+        <v>0.2395</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6235000000000001</v>
+        <v>-0.1473</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0425</v>
+        <v>0.3868</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.0713</v>
+        <v>-0.9405</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.0713</v>
+        <v>0.266</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>C. POYATOS PARRA</t>
+          <t>X. ANDREU GARI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3982</v>
+        <v>0.8704</v>
       </c>
       <c r="E19" t="n">
-        <v>3.0188</v>
+        <v>0.8065</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.6207</v>
+        <v>0.0639</v>
       </c>
       <c r="G19" t="n">
-        <v>1.6995</v>
+        <v>-0.4655</v>
       </c>
       <c r="H19" t="n">
-        <v>1.4325</v>
+        <v>-0.6403</v>
       </c>
       <c r="I19" t="n">
-        <v>0.267</v>
+        <v>0.1748</v>
       </c>
       <c r="J19" t="n">
-        <v>3.1357</v>
+        <v>-0.6292</v>
       </c>
       <c r="K19" t="n">
-        <v>2.8947</v>
+        <v>-1.1991</v>
       </c>
       <c r="L19" t="n">
-        <v>0.241</v>
+        <v>0.5699</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.4362</v>
+        <v>0.1637</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.4622</v>
+        <v>0.5588</v>
       </c>
       <c r="O19" t="n">
-        <v>0.026</v>
+        <v>-0.3951</v>
       </c>
       <c r="P19" t="n">
-        <v>1.3887</v>
+        <v>1.1903</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9919</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.3806</v>
+        <v>1.1903</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7347</v>
+        <v>-0.4577</v>
       </c>
       <c r="T19" t="n">
-        <v>0.6803</v>
+        <v>-0.374</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0544</v>
+        <v>-0.0837</v>
       </c>
       <c r="V19" t="n">
-        <v>-3.4247</v>
+        <v>0.6032</v>
       </c>
       <c r="W19" t="n">
-        <v>0.1947</v>
+        <v>1.8097</v>
       </c>
       <c r="X19" t="n">
-        <v>-3.6194</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. OCHOGAVIA CIFRE</t>
+          <t>C. POYATOS PARRA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1912</v>
+        <v>0.0206</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.6515</v>
+        <v>2.3046</v>
       </c>
       <c r="F20" t="n">
-        <v>1.8428</v>
+        <v>-2.284</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.0701</v>
+        <v>1.6995</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.0028</v>
+        <v>1.4325</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.0673</v>
+        <v>0.267</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.9829</v>
+        <v>3.1357</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.624</v>
+        <v>2.8947</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.3589</v>
+        <v>0.241</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.0872</v>
+        <v>-1.4362</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.3788</v>
+        <v>-1.4622</v>
       </c>
       <c r="O20" t="n">
-        <v>0.2916</v>
+        <v>0.026</v>
       </c>
       <c r="P20" t="n">
-        <v>2.1822</v>
+        <v>1.3887</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-0.9919</v>
       </c>
       <c r="R20" t="n">
-        <v>2.1822</v>
+        <v>2.3806</v>
       </c>
       <c r="S20" t="n">
-        <v>1.9006</v>
+        <v>0.3572</v>
       </c>
       <c r="T20" t="n">
-        <v>0.6803</v>
+        <v>-0.0339</v>
       </c>
       <c r="U20" t="n">
-        <v>1.2202</v>
+        <v>0.391</v>
       </c>
       <c r="V20" t="n">
-        <v>-2.8215</v>
+        <v>-3.4247</v>
       </c>
       <c r="W20" t="n">
-        <v>-1.349</v>
+        <v>0.1947</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.4724</v>
+        <v>-3.6194</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X. ANDREU GARI</t>
+          <t>M. OCHOGAVIA CIFRE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0057</v>
+        <v>-0.4694</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1943</v>
+        <v>-2.0597</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.1886</v>
+        <v>1.5903</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.4655</v>
+        <v>-1.0701</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.6403</v>
+        <v>-1.0028</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1748</v>
+        <v>-0.0673</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.6292</v>
+        <v>-0.9829</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.1991</v>
+        <v>-0.624</v>
       </c>
       <c r="L21" t="n">
-        <v>0.5699</v>
+        <v>-0.3589</v>
       </c>
       <c r="M21" t="n">
-        <v>0.1637</v>
+        <v>-0.0872</v>
       </c>
       <c r="N21" t="n">
-        <v>0.5588</v>
+        <v>-0.3788</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.3951</v>
+        <v>0.2916</v>
       </c>
       <c r="P21" t="n">
-        <v>1.1903</v>
+        <v>2.1822</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1903</v>
+        <v>2.1822</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.3223</v>
+        <v>1.2399</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.9862</v>
+        <v>0.2722</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3362</v>
+        <v>0.9677</v>
       </c>
       <c r="V21" t="n">
-        <v>0.6032</v>
+        <v>-2.8215</v>
       </c>
       <c r="W21" t="n">
-        <v>1.8097</v>
+        <v>-1.349</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.2065</v>
+        <v>-1.4724</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.4533</v>
+        <v>-0.8514</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.3471</v>
+        <v>-0.6329</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.1062</v>
+        <v>-0.2184</v>
       </c>
       <c r="G22" t="n">
         <v>1.7369</v>
@@ -2170,13 +2170,13 @@
         <v>2.1822</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0352</v>
+        <v>0.5668</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.9975000000000001</v>
+        <v>-0.2833</v>
       </c>
       <c r="U22" t="n">
-        <v>0.9624</v>
+        <v>0.8501</v>
       </c>
       <c r="V22" t="n">
         <v>-3.3534</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.2587</v>
+        <v>-1.8148</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.3263</v>
+        <v>-1.7141</v>
       </c>
       <c r="F23" t="n">
-        <v>0.06759999999999999</v>
+        <v>-0.1007</v>
       </c>
       <c r="G23" t="n">
         <v>-1.4388</v>
@@ -2248,13 +2248,13 @@
         <v>0.9919</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.6054</v>
+        <v>-0.1615</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.9238</v>
+        <v>-0.3117</v>
       </c>
       <c r="U23" t="n">
-        <v>0.3184</v>
+        <v>0.1501</v>
       </c>
       <c r="V23" t="n">
         <v>-1.2065</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.8303</v>
+        <v>-3.0828</v>
       </c>
       <c r="E24" t="n">
         <v>-2.3714</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.4589</v>
+        <v>-0.7114</v>
       </c>
       <c r="G24" t="n">
         <v>-1.479</v>
@@ -2326,13 +2326,13 @@
         <v>1.1903</v>
       </c>
       <c r="S24" t="n">
-        <v>0.8632</v>
+        <v>0.6107</v>
       </c>
       <c r="T24" t="n">
         <v>0.0567</v>
       </c>
       <c r="U24" t="n">
-        <v>0.8065</v>
+        <v>0.554</v>
       </c>
       <c r="V24" t="n">
         <v>-2.4129</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>9.740400000000003</v>
+        <v>9.740400000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>6.341900000000001</v>
+        <v>6.341900000000003</v>
       </c>
       <c r="F25" t="n">
-        <v>3.398600000000001</v>
+        <v>3.3987</v>
       </c>
       <c r="G25" t="n">
         <v>11.9752</v>
@@ -2374,7 +2374,7 @@
         <v>2.6475</v>
       </c>
       <c r="I25" t="n">
-        <v>9.3277</v>
+        <v>9.327699999999998</v>
       </c>
       <c r="J25" t="n">
         <v>15.3461</v>
@@ -2407,7 +2407,7 @@
         <v>2.8342</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.3878</v>
+        <v>-1.3877</v>
       </c>
       <c r="U25" t="n">
         <v>4.222</v>
